--- a/E-commerce_Retail_Sales/PC_Tech_Profit_Maximization/PC_Tech_Modelling_Financials_to_Maximize_Profit.xlsx
+++ b/E-commerce_Retail_Sales/PC_Tech_Profit_Maximization/PC_Tech_Modelling_Financials_to_Maximize_Profit.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\E-commerce_Retail_Sales\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\E-commerce_Retail_Sales\PC_Tech_Profit_Maximization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9143CF83-FA90-4BC4-820E-8C716EE4095F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75B8373-D270-4E08-9F5D-7EB06EFD599E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{194C89C8-78F5-47C7-AFE4-4490EB54D73F}"/>
   </bookViews>
@@ -166,7 +166,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -244,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -262,20 +262,19 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -359,7 +358,7 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-IN" sz="1100" baseline="0"/>
-            <a:t>The PC Tech Company shoudl produce 560 units of Basic computers and 1200 units of XP computers to maximize profit.</a:t>
+            <a:t>The PC Tech Company should produce 560 units of Basic computers and 1200 units of XP computers to maximize profit.</a:t>
           </a:r>
           <a:endParaRPr lang="en-IN" sz="1100"/>
         </a:p>
@@ -927,10 +926,10 @@
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="14">
         <v>560</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="14">
         <v>1200</v>
       </c>
       <c r="D2" s="1"/>
@@ -1287,10 +1286,10 @@
       <c r="W14" s="1"/>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="12">
         <f>SUMPRODUCT(B2:C2,B11:C11)+ SUMPRODUCT(B2:C2,B3:C3,B13:C13)+SUMPRODUCT(B2:C2,B4:C4,B14:C14)</f>
         <v>508400</v>
       </c>
@@ -1339,7 +1338,7 @@
       <c r="W16" s="1"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="8"/>
@@ -1400,7 +1399,7 @@
       <c r="A19" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="13">
         <f>SUMPRODUCT(B2:C2,B18:C18)</f>
         <v>708000</v>
       </c>

--- a/E-commerce_Retail_Sales/PC_Tech_Profit_Maximization/PC_Tech_Modelling_Financials_to_Maximize_Profit.xlsx
+++ b/E-commerce_Retail_Sales/PC_Tech_Profit_Maximization/PC_Tech_Modelling_Financials_to_Maximize_Profit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\E-commerce_Retail_Sales\PC_Tech_Profit_Maximization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75B8373-D270-4E08-9F5D-7EB06EFD599E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA5F31C-8174-4656-A25F-2E3F1E524369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{194C89C8-78F5-47C7-AFE4-4490EB54D73F}"/>
   </bookViews>
@@ -1659,6 +1659,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <cellWatches>
+    <cellWatch r="B6"/>
+  </cellWatches>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
